--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -295,7 +295,7 @@
     <t xml:space="preserve">P2 medio</t>
   </si>
   <si>
-    <t xml:space="preserve">Sem historico nao ha painel. Historico nao se cria retroativamente.</t>
+    <t xml:space="preserve">Sem historico nao ha painel. Historico nao se cria retroativamente. Espera o RLS do Dr. Code.</t>
   </si>
   <si>
     <t xml:space="preserve">Catalogo de modulos com precos</t>
@@ -421,7 +421,7 @@
     <t xml:space="preserve">SPF e DKIM para padaxor.com.br. Hoje o remetente e da ferramenta e o Gmail marca como golpe.</t>
   </si>
   <si>
-    <t xml:space="preserve">Convite de licenciado chegando com tarja vermelha de phishing destroi confianca.</t>
+    <t xml:space="preserve">Convite de licenciado chegando com tarja vermelha de phishing destroi confianca. Espera o Cloudflare.</t>
   </si>
   <si>
     <t xml:space="preserve">railway.toml versionado</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">7</t>
   </si>
   <si>
-    <t xml:space="preserve">Hoje ha espelho. Espelho e transicao, nao destino.</t>
+    <t xml:space="preserve">Hoje ha espelho. Espelho e transicao, nao destino. Liberado: o item 7 ficou concluido.</t>
   </si>
   <si>
     <t xml:space="preserve">Suite de testes e integracao continua</t>
@@ -1887,31 +1887,31 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="F22" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2206,31 +2206,31 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="5" t="s">
+      <c r="F33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="6" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2264,31 +2264,31 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35" s="6" t="s">
+      <c r="F35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="5" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C44" s="9" t="n">
         <f aca="false">COUNTIF(F5:F40,"A FAZER")</f>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C45" s="9" t="n">
         <f aca="false">COUNTIF(F5:F40,"AGUARDANDO")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -14,7 +14,7 @@
     <sheet name="LEIA-ME" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$I$40</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$I$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="258">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -208,7 +208,7 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">Resolve travessia de sessao, caixa nativa e 'encerrar sessao' de uma vez.</t>
+    <t xml:space="preserve">Entregue 30/07 no commit 3a38349, conferido: pages/login/index.tsx criado e CollaboratorGate passou a redirecionar.</t>
   </si>
   <si>
     <t xml:space="preserve">Site vira botao, nao segundo login</t>
@@ -220,36 +220,36 @@
     <t xml:space="preserve">11</t>
   </si>
   <si>
+    <t xml:space="preserve">1h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIBERADO em 30/07: a tela do item 11 existe. Elimina o segundo formulario de autenticacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNS do padaxor.com.br no Cloudflare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar os servidores de nome no Registro.br pelos do Cloudflare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Railway exige CNAME Flattening ou ALIAS para dominio raiz. Registro.br nao faz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominio proprio apontando para o sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">app.padaxor.com.br no Railway com certificado automatico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGUARDANDO</t>
   </si>
   <si>
-    <t xml:space="preserve">1h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elimina o segundo formulario de autenticacao e o fluxo de conta no site.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNS do padaxor.com.br no Cloudflare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar os servidores de nome no Registro.br pelos do Cloudflare.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Railway exige CNAME Flattening ou ALIAS para dominio raiz. Registro.br nao faz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominio proprio apontando para o sistema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">app.padaxor.com.br no Railway com certificado automatico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
     <t xml:space="preserve">Depende do passo do Cloudflare.</t>
   </si>
   <si>
@@ -259,7 +259,10 @@
     <t xml:space="preserve">O painel do sistema ainda exibe PAXTER na identidade visual.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nome oficial: PADAXOR. Motor: PAWARDS. PADCOM e outra empresa.</t>
+    <t xml:space="preserve">parcial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titulo da aba e do aplicativo entregues 30/07 no commit 3a38349. As telas internas seguem no item 38.</t>
   </si>
   <si>
     <t xml:space="preserve">Porta da area do paciente</t>
@@ -500,6 +503,24 @@
   </si>
   <si>
     <t xml:space="preserve">Perfil: executa missao inteira de ponta a ponta. Candidato natural: item 32 ou 33.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditoria de rotas: consulta sem filtro de empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varredura de todas as rotas da API listando consulta que le tabela clinica sem restringir por empresa. Entrega e a lista, nao a correcao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideia do Dr. Replit, territorio dele (rotas de API) e nao toca o banco. A lista e a entrada do item 9: sem ela o RLS e escrito as cegas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca PAXTER para PADAXOR nas telas internas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restante do rebrand: textos dentro do painel, nao so o titulo da aba entregue no item 15.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O nome oficial PADAXOR ja esta decidido pelo CEO. O Dr. Replit havia marcado como decisao pendente; nao e, o nome ja foi batido.</t>
   </si>
   <si>
     <t xml:space="preserve">RESUMO</t>
@@ -1324,7 +1345,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1684,61 +1705,61 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="H16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="6" t="s">
+      <c r="I16" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1746,10 +1767,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>21</v>
@@ -1764,10 +1785,10 @@
         <v>38</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1775,57 +1796,57 @@
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="F19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>77</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1833,10 +1854,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>37</v>
@@ -1851,10 +1872,10 @@
         <v>38</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1862,10 +1883,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>25</v>
@@ -1880,10 +1901,10 @@
         <v>38</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1891,28 +1912,28 @@
         <v>18</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1920,10 +1941,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>21</v>
@@ -1935,13 +1956,13 @@
         <v>45</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1949,28 +1970,28 @@
         <v>20</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1978,28 +1999,28 @@
         <v>21</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2007,28 +2028,28 @@
         <v>22</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>46</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2036,28 +2057,28 @@
         <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2065,28 +2086,28 @@
         <v>24</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2094,28 +2115,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2123,10 +2144,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>21</v>
@@ -2138,13 +2159,13 @@
         <v>45</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2152,28 +2173,28 @@
         <v>27</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="G31" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>55</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2181,28 +2202,28 @@
         <v>28</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2210,19 +2231,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>38</v>
@@ -2231,7 +2252,7 @@
         <v>46</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2239,10 +2260,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>25</v>
@@ -2254,13 +2275,13 @@
         <v>45</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2268,28 +2289,28 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2297,28 +2318,28 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2326,28 +2347,28 @@
         <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2355,10 +2376,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>21</v>
@@ -2370,13 +2391,13 @@
         <v>45</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2384,10 +2405,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>25</v>
@@ -2399,13 +2420,13 @@
         <v>45</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2413,83 +2434,141 @@
         <v>36</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>14</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="8" t="s">
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C43" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F40,"CONCLUIDO")</f>
-        <v>7</v>
+      <c r="C41" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C44" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F40,"A FAZER")</f>
-        <v>16</v>
+      <c r="B44" s="7" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="8" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C45" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F40,"AGUARDANDO")</f>
-        <v>13</v>
+        <f aca="false">COUNTIF(F5:F42,"CONCLUIDO")</f>
+        <v>9</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="8" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C46" s="9" t="n">
-        <f aca="false">COUNTA(A5:A40)</f>
-        <v>36</v>
+        <f aca="false">COUNTIF(F5:F42,"A FAZER")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <f aca="false">COUNTIF(F5:F42,"AGUARDANDO")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <f aca="false">COUNTA(A5:A42)</f>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I40"/>
+  <autoFilter ref="A4:I42"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F40" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F42" type="list">
       <formula1>"A FAZER,EM CURSO,AGUARDANDO,CONCLUIDO,CANCELADO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G40" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G42" type="list">
       <formula1>"P0 critico,P1 alto,P2 medio,P3 baixo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2521,7 +2600,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2530,7 +2609,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2539,19 +2618,19 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2559,16 +2638,16 @@
         <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2576,33 +2655,33 @@
         <v>25</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2610,43 +2689,43 @@
         <v>37</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2655,7 +2734,7 @@
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2664,7 +2743,7 @@
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2673,7 +2752,7 @@
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -2682,7 +2761,7 @@
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2726,7 +2805,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2735,7 +2814,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2747,16 +2826,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2764,13 +2843,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -2779,13 +2858,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -2794,13 +2873,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7" s="12"/>
     </row>
@@ -2809,13 +2888,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" s="12"/>
     </row>
@@ -2824,13 +2903,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -2839,13 +2918,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -2854,13 +2933,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -2869,13 +2948,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -2884,13 +2963,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -2899,36 +2978,36 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -2960,78 +3039,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -12,8 +12,11 @@
     <sheet name="MATRIZ DA EQUIPE" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="DECISOES DO CEO" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="LEIA-ME" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="REGRAS DE EDICAO" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="HISTORICO" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$14</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$I$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="333">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -800,6 +803,231 @@
   </si>
   <si>
     <t xml:space="preserve">O sistema ja se chamou PAWARDS, depois PAXTER, depois PARXIS. Hoje e PADAXOR, com dominio proprio padaxor.com.br registrado em 27/07/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PADAXOR — Regras de edicao desta planilha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vale para todo mundo: CEO, Dr. Code, Dr. Replit, Dr. Lovable e Dr. Manus. A regra mestra e uma: NADA SE APAGA, tudo se acrescenta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que pode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que nao pode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por que</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nada se apaga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acrescentar linha, acrescentar observacao, acrescentar comentario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apagar linha, apagar texto de outra pessoa, sobrescrever celula que ja tinha conteudo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So se consegue comparar o que foi pedido, o que foi feito e o que foi corrigido se o antes continuar existindo. E o Art. 56 da Biblia: log append-only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero de item e permanente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criar item novo com numero maior que o ultimo em uso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaproveitar, reatribuir ou renumerar numero que ja existe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em 30/07/2026 uma segunda fila reatribuiu os numeros 8 a 31 e os numeros 11 e 15 passaram a significar duas coisas. Um recado dizendo 'comece o item 11' ficou impossivel de obedecer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mudanca de estado vira linha no HISTORICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mudar a coluna Estado e registrar na aba HISTORICO: data, quem, de que para que, e por que.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mudar Estado sem deixar rastro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem o rastro ninguem sabe se o item foi concluido, corrigido ou apagado por engano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concluido exige prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcar CONCLUIDO citando o hash do commit e o arquivo tocado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcar CONCLUIDO por prosa, memoria ou intencao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 19 da Biblia: onda so fecha com hash no GitHub mais caso real testado. Anunciar sem prova e fantasia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada um na sua coluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualquer agente escreve na coluna Observacao, assinando com nome e data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um agente mudar Responsavel, Depende de ou Prioridade de item de outro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Territorio esta na aba MATRIZ DA EQUIPE. Foi a fronteira que faltou quando dois agentes consertaram o mesmo arquivo tres vezes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um escritor da estrutura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedir mudanca de estrutura pela coluna Observacao ou pelo recado no repositorio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dois agentes gerando a planilha ou subindo arquivo de mesmo nome para o Drive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurso compartilhado com dois escritores corrompe em silencio: foi o drizzle.config.ts, e depois foi esta propria planilha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As duas copias dizem a mesma coisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ler no Drive (CEO) ou no repositorio em docs/LINHA_DE_PRODUCAO (agentes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Editar so uma das duas e deixar a outra velha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O espelho em texto e gerado desta planilha por script, nunca digitado a mao. Divergiu = alguem digitou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisao do CEO e so do CEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualquer um pode registrar uma pergunta na aba DECISOES DO CEO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualquer agente responder no lugar dele preco, plano ou decisao clinica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 15 da Biblia, balde vermelho. Preco e decisao clinica nascem do cacique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PADAXOR — Historico de mudancas (append-only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So cresce. Linha nunca se apaga nem se corrige: mudou de novo, entra linha nova. Ordem cronologica, mais antigo em cima.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como estava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como ficou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por que mudou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 itens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primeira versao da fila. Existe porque tres vezes dois agentes consertaram o mesmo arquivo sem saber um do outro e o git aceitou os dois lados sem conflito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR #6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erro meu: a dependencia (item 7) ja estava concluida. O estado errado escondia trabalho livre do Dr. Lovable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conferir_coerencia.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erro meu, inverso do anterior: aparecia livre, mas espera o RLS (item 9), que e do Dr. Code. O dono poderia comecar em cima de dependencia de outro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesmo erro do item 18: espera o Cloudflare (item 13), que e do CEO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela de login dedicada entregue. Conferido no codigo, nao aceito em prosa: pages/login/index.tsx criado e CollaboratorGate passou a redirecionar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit 3a38349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titulo da aba e do aplicativo corrigidos. Entrega parcial: as telas internas seguem no item 38.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liberado por consequencia: a tela do item 11 que o Dr. Lovable esperava passou a existir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item novo, ideia do Dr. Replit: auditoria de rotas sem filtro de empresa. Entrou como 37 e nao como 9 ou 10 porque esses numeros ja significam outra coisa desde 29/07.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLISAO_DE_NUMERACAO_26.07.30.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item novo: resto do rebrand nas telas internas, que o item 15 comecou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estrutura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 abas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 abas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido do CEO: as regras passam a morar dentro do proprio arquivo, e o historico passa a registrar o antes e o depois de cada mudanca. Abas REGRAS DE EDICAO e HISTORICO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acrescente aqui</t>
   </si>
 </sst>
 </file>
@@ -810,7 +1038,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -885,6 +1113,14 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF9A6B28"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF9A8F7E"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -983,7 +1219,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1048,6 +1284,14 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1057,7 +1301,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1093,6 +1337,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F2EA"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1147,7 +1399,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF6B5F4E"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF9A8F7E"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1162,6 +1414,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -3126,4 +3382,530 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H14"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -14,10 +14,12 @@
     <sheet name="LEIA-ME" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="REGRAS DE EDICAO" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="HISTORICO" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="GLOSSARIO" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">GLOSSARIO!$A$4:$E$38</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$14</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$I$42</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="548">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -64,6 +66,9 @@
     <t xml:space="preserve">Observacao</t>
   </si>
   <si>
+    <t xml:space="preserve">Em linguagem de leigo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Banco em producao com dados reais</t>
   </si>
   <si>
@@ -88,6 +93,9 @@
     <t xml:space="preserve">Volumetria conferida por contagem no banco de producao.</t>
   </si>
   <si>
+    <t xml:space="preserve">Os dados reais dos seus clientes sairam do computador antigo e entraram no novo. Como mudar o arquivo de papel de uma clinica para outra sala: 3.683 fichas e 24.287 exames, todos conferidos um a um na chegada.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Backup do Postgres</t>
   </si>
   <si>
@@ -100,6 +108,9 @@
     <t xml:space="preserve">Salvou a carga quando o primeiro TRUNCATE ficou confirmado no meio.</t>
   </si>
   <si>
+    <t xml:space="preserve">Copia de seguranca automatica do banco, todo dia, toda semana, todo mes. E o seguro contra incendio: voce paga sem usar, e no dia do incendio ele e a unica coisa que importa. Ja salvou uma carga que travou no meio.</t>
+  </si>
+  <si>
     <t xml:space="preserve">api-server no ar com dominio e CORS</t>
   </si>
   <si>
@@ -112,6 +123,9 @@
     <t xml:space="preserve">ALLOWED_ORIGINS estava com valor invalido ['https://','https://'].</t>
   </si>
   <si>
+    <t xml:space="preserve">O servidor que atende os pedidos do sistema esta no ar, com endereco proprio na internet e a lista de quem pode chamar ele configurada corretamente.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Login do CEO funcionando</t>
   </si>
   <si>
@@ -124,6 +138,9 @@
     <t xml:space="preserve">Causa da falha: dois verifyPassword com formato identico e derivacao incompativel.</t>
   </si>
   <si>
+    <t xml:space="preserve">Sua senha de entrada no sistema foi gravada no formato certo e testada em producao. Antes disso ela existia mas o sistema nao a reconhecia.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Token de colaborador vale no perimetro</t>
   </si>
   <si>
@@ -136,6 +153,9 @@
     <t xml:space="preserve">PR #5. Senha unica compartilhada nao escala para licenciados.</t>
   </si>
   <si>
+    <t xml:space="preserve">O cracha do colaborador passou a ser aceito nas portas internas. Antes o cracha existia mas o porteiro nao olhava para ele.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Site publicado com as 6 correcoes</t>
   </si>
   <si>
@@ -151,6 +171,9 @@
     <t xml:space="preserve">Cadastro publico e OAuth removidos: elimina conta acidental e email marcado como golpe.</t>
   </si>
   <si>
+    <t xml:space="preserve">O site publico foi corrigido em seis pontos, entre eles tirar o cadastro aberto, que deixava qualquer um criar conta sozinho.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Captacao de interessados</t>
   </si>
   <si>
@@ -160,6 +183,9 @@
     <t xml:space="preserve">11 testes aprovados contra producao.</t>
   </si>
   <si>
+    <t xml:space="preserve">Quando alguem se interessa pelo produto no site, o nome e o contato agora caem numa lista dentro do sistema, em vez de se perderem.</t>
+  </si>
+  <si>
     <t xml:space="preserve">empresa_id na tabela professionals</t>
   </si>
   <si>
@@ -175,6 +201,9 @@
     <t xml:space="preserve">Primeira coisa que quebra ao licenciar a segunda clinica.</t>
   </si>
   <si>
+    <t xml:space="preserve">Hoje um colaborador nao esta amarrado a nenhuma clinica: ele so existe solto. Isso e uma coluna nova no banco dizendo 'este colaborador pertence a esta clinica'. E o CPF do vinculo. Sem ela, ao vender para a segunda clinica, ninguem sabe quem e de quem.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Isolamento entre clinicas no banco (RLS)</t>
   </si>
   <si>
@@ -190,6 +219,9 @@
     <t xml:space="preserve">Uma clausula WHERE esquecida = uma clinica vendo paciente de outra. Zero politicas hoje.</t>
   </si>
   <si>
+    <t xml:space="preserve">Trava no proprio banco de dados que impede uma clinica de ver paciente de outra, mesmo que o programador esqueca de filtrar. Hoje a separacao depende do programador lembrar toda vez; isso troca a memoria humana por uma tranca de verdade. Hoje ha zero trancas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marca distinta nos dois esquemas de senha</t>
   </si>
   <si>
@@ -202,6 +234,9 @@
     <t xml:space="preserve">Os dois gravam scrypt$ hoje. Foi a armadilha que custou uma noite inteira.</t>
   </si>
   <si>
+    <t xml:space="preserve">Existem dois tipos de senha no sistema, guardados de jeitos diferentes, mas gravados com a MESMA etiqueta. E como dois frascos de remedio com o mesmo rotulo e conteudo diferente. Foi isso que fez seu login falhar por uma noite inteira. Isso poe rotulo diferente em cada frasco.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tela de login dentro do padaxor</t>
   </si>
   <si>
@@ -214,6 +249,9 @@
     <t xml:space="preserve">Entregue 30/07 no commit 3a38349, conferido: pages/login/index.tsx criado e CollaboratorGate passou a redirecionar.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tela de entrada propria do sistema, em vez da caixinha cinza do navegador. Ja entregue em 30/07.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Site vira botao, nao segundo login</t>
   </si>
   <si>
@@ -229,6 +267,9 @@
     <t xml:space="preserve">LIBERADO em 30/07: a tela do item 11 existe. Elimina o segundo formulario de autenticacao.</t>
   </si>
   <si>
+    <t xml:space="preserve">O botao Entrar do site deixa de pedir senha por conta propria e passa a levar a pessoa para a tela de entrada do sistema. Uma porta so em vez de duas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DNS do padaxor.com.br no Cloudflare</t>
   </si>
   <si>
@@ -241,6 +282,9 @@
     <t xml:space="preserve">Railway exige CNAME Flattening ou ALIAS para dominio raiz. Registro.br nao faz.</t>
   </si>
   <si>
+    <t xml:space="preserve">Trocar quem cuida do endereco padaxor.com.br na internet. O registrador brasileiro nao faz um recurso que o servidor precisa; o Cloudflare faz, e e de graca.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dominio proprio apontando para o sistema</t>
   </si>
   <si>
@@ -256,6 +300,9 @@
     <t xml:space="preserve">Depende do passo do Cloudflare.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fazer app.padaxor.com.br apontar para o sistema, com cadeado de seguranca automatico no navegador.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marca PAXTER para PADAXOR no painel</t>
   </si>
   <si>
@@ -268,6 +315,9 @@
     <t xml:space="preserve">Titulo da aba e do aplicativo entregues 30/07 no commit 3a38349. As telas internas seguem no item 38.</t>
   </si>
   <si>
+    <t xml:space="preserve">O painel ainda mostrava o nome antigo PAXTER. Titulo da aba corrigido em 30/07; o resto das telas segue no item 38.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Porta da area do paciente</t>
   </si>
   <si>
@@ -280,6 +330,9 @@
     <t xml:space="preserve">Quarta porta do produto inteira sem macaneta.</t>
   </si>
   <si>
+    <t xml:space="preserve">O servidor ja tem doze portas prontas para a area do paciente, mas o site nao tem nenhum botao que leve ate elas. E uma porta inteira construida e sem macaneta.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Indice unico em lower(login_username)</t>
   </si>
   <si>
@@ -289,6 +342,9 @@
     <t xml:space="preserve">Prevencao. Nao foi a causa do bug de hoje — nao havia duplicata.</t>
   </si>
   <si>
+    <t xml:space="preserve">Impedir que dois colaboradores tenham o mesmo nome de usuario. Prevencao: nao foi a causa do problema de hoje, mas seria a causa do de amanha.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ligar o registro de consumo</t>
   </si>
   <si>
@@ -304,6 +360,9 @@
     <t xml:space="preserve">Sem historico nao ha painel. Historico nao se cria retroativamente. Espera o RLS do Dr. Code.</t>
   </si>
   <si>
+    <t xml:space="preserve">Comecar a anotar quanto cada clinica usa do sistema. Sem anotar desde ja, nao existe historico depois: historico nao se cria para tras.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Catalogo de modulos com precos</t>
   </si>
   <si>
@@ -316,6 +375,9 @@
     <t xml:space="preserve">Os valores sao decisao do CEO. Nada vai para tela sem eles.</t>
   </si>
   <si>
+    <t xml:space="preserve">Definir quanto custa cada modulo em reais. So voce decide. Nenhum preco vai para tela sem isso.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Menu com modulos travados</t>
   </si>
   <si>
@@ -328,6 +390,9 @@
     <t xml:space="preserve">Coracao do modelo comercial. Depende do catalogo e dos precos.</t>
   </si>
   <si>
+    <t xml:space="preserve">Os modulos que a clinica nao comprou aparecem apagados com um cadeado, e clicar abre a oferta. E a vitrine da loja: voce ve o que nao comprou, e isso e o que faz querer comprar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mensagem de desejo com 48h e indicacao</t>
   </si>
   <si>
@@ -340,6 +405,9 @@
     <t xml:space="preserve">Mensalidade nunca muda — desconto so na entrada.</t>
   </si>
   <si>
+    <t xml:space="preserve">A mensagem que aparece ao clicar no cadeado: o que o modulo faz, o preco promocional valendo 48 horas, o valor cheio riscado e o desconto por indicacao.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Login de licenciado (o segundo chapeu)</t>
   </si>
   <si>
@@ -349,6 +417,9 @@
     <t xml:space="preserve">Dois logins, mesma clinica, lentes diferentes. Pagamento real de R$ 1 via Asaas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Um segundo usuario seu, entrando na mesma clinica, mas enxergando so o que um cliente enxergaria. Dois cracha, mesma porta, oculos diferentes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Painel do CEO com seletor de clinica</t>
   </si>
   <si>
@@ -358,6 +429,9 @@
     <t xml:space="preserve">tenantContext ja modela isPlatformOwner + empresaId. Comecar somente-leitura nas outras clinicas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Painel onde voce ve todas as clinicas de uma vez e consegue entrar na visao de cada dona para ver o que ela ve.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Painel de bilhetagem</t>
   </si>
   <si>
@@ -373,6 +447,9 @@
     <t xml:space="preserve">Sem fornecedor novo. Com 12 clinicas o Postgres aguenta com folga.</t>
   </si>
   <si>
+    <t xml:space="preserve">Painel de quanto cada clinica consumiu, por periodo e por tipo, atualizando sozinho na tela.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Upsell por limiar de uso</t>
   </si>
   <si>
@@ -385,6 +462,9 @@
     <t xml:space="preserve">Oferece quando o uso prova que faz sentido. Observacao honesta, nao pressao.</t>
   </si>
   <si>
+    <t xml:space="preserve">Quando o uso de um modulo passa de um limite, o sistema oferece o upgrade sozinho. Oferece quando o proprio uso ja provou que faz sentido, nao antes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zoho configurado</t>
   </si>
   <si>
@@ -397,6 +477,9 @@
     <t xml:space="preserve">Precisa da conta Zoho e do token. Depois disso o sistema cria sozinho.</t>
   </si>
   <si>
+    <t xml:space="preserve">Configurar a conta de e-mail corporativo. Depois disso o sistema cria os e-mails de cada clinica nova sozinho.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DNS automatico via Cloudflare API</t>
   </si>
   <si>
@@ -406,6 +489,9 @@
     <t xml:space="preserve">Depende do Cloudflare ser o provedor de DNS.</t>
   </si>
   <si>
+    <t xml:space="preserve">Quando uma clinica nova e ativada, o endereco de internet dela e criado sozinho, sem ninguem abrir painel nenhum.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tela de linha de producao de clinica</t>
   </si>
   <si>
@@ -421,6 +507,9 @@
     <t xml:space="preserve">COBRAR ANTES DE PROVISIONAR: pendurar no webhook do Asaas, nao antes dele.</t>
   </si>
   <si>
+    <t xml:space="preserve">A esteira que transforma um contrato assinado em clinica funcionando: nome, endereco, e-mails, site. Regra importante: cobrar antes de montar, nunca depois.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Autenticacao de email em dominio proprio</t>
   </si>
   <si>
@@ -430,6 +519,9 @@
     <t xml:space="preserve">Convite de licenciado chegando com tarja vermelha de phishing destroi confianca. Espera o Cloudflare.</t>
   </si>
   <si>
+    <t xml:space="preserve">Assinatura digital do seu dominio no e-mail. Sem ela o Gmail marca seu convite como golpe, com tarja vermelha. Convite de socio chegando como phishing destroi a confianca antes da primeira conversa.</t>
+  </si>
+  <si>
     <t xml:space="preserve">railway.toml versionado</t>
   </si>
   <si>
@@ -442,6 +534,9 @@
     <t xml:space="preserve">Hoje a configuracao vive so no painel. Se o projeto sumir, o codigo nao reconstroi o sistema.</t>
   </si>
   <si>
+    <t xml:space="preserve">Escrever no proprio codigo como o sistema e montado. Hoje isso so existe dentro do painel de um fornecedor: se a conta sumir, o codigo sozinho nao remonta o sistema.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colapsar o Supabase</t>
   </si>
   <si>
@@ -454,6 +549,9 @@
     <t xml:space="preserve">Hoje ha espelho. Espelho e transicao, nao destino. Liberado: o item 7 ficou concluido.</t>
   </si>
   <si>
+    <t xml:space="preserve">Hoje o formulario do site grava em dois lugares ao mesmo tempo. Isso desliga o lugar antigo e deixa so um. Espelho e etapa de mudanca, nao destino.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Suite de testes e integracao continua</t>
   </si>
   <si>
@@ -466,6 +564,9 @@
     <t xml:space="preserve">Hoje: nenhum CI, nenhum script de teste no api-server, 1 arquivo de teste no repo inteiro.</t>
   </si>
   <si>
+    <t xml:space="preserve">Testes automaticos que rodam sozinhos antes de publicar e barram o erro antes de ele chegar no ar. Hoje nao existe nenhum: por isso os erros das ultimas horas so apareceram em producao.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Renomear padcom para padaxor internamente</t>
   </si>
   <si>
@@ -478,6 +579,9 @@
     <t xml:space="preserve">So com todos parados. O caminho de build vive no painel do Railway, fora do repo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Trocar o nome interno antigo por PADAXOR em 414 arquivos. So da para fazer com todos os agentes parados, senao um atropela o outro.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Planos de paciente</t>
   </si>
   <si>
@@ -487,6 +591,9 @@
     <t xml:space="preserve">Prazo de resposta vira obrigacao contratual. Precisa desenho, nao improviso.</t>
   </si>
   <si>
+    <t xml:space="preserve">Definir os niveis de acompanhamento do paciente e o que cada nivel entrega. Cuidado: prazo de resposta prometido vira obrigacao de contrato.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Identificador de requisicao e contrato da API</t>
   </si>
   <si>
@@ -496,6 +603,9 @@
     <t xml:space="preserve">Ideia veio do Dr. Lovable; quem executa e o Dr. Code (e servidor). Acaba com reclamacao sem rastro.</t>
   </si>
   <si>
+    <t xml:space="preserve">Dar um numero de protocolo a cada chamada do sistema. Igual ao numero de atendimento do banco: quando alguem reclama, existe o numero para achar o que aconteceu.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Missao a definir para o Dr. Manus</t>
   </si>
   <si>
@@ -508,6 +618,9 @@
     <t xml:space="preserve">Perfil: executa missao inteira de ponta a ponta. Candidato natural: item 32 ou 33.</t>
   </si>
   <si>
+    <t xml:space="preserve">Vaga aberta para o Dr. Manus, que executa missao inteira sozinho. Ainda sem frente definida nesta fase.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Auditoria de rotas: consulta sem filtro de empresa</t>
   </si>
   <si>
@@ -517,6 +630,9 @@
     <t xml:space="preserve">Ideia do Dr. Replit, territorio dele (rotas de API) e nao toca o banco. A lista e a entrada do item 9: sem ela o RLS e escrito as cegas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Varrer todas as portas do sistema procurando as que leem dados sem perguntar de qual clinica. A entrega e a LISTA dos buracos, nao o conserto. E o exame antes da cirurgia: sem a lista, o item 9 seria operado as cegas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marca PAXTER para PADAXOR nas telas internas</t>
   </si>
   <si>
@@ -526,6 +642,9 @@
     <t xml:space="preserve">O nome oficial PADAXOR ja esta decidido pelo CEO. O Dr. Replit havia marcado como decisao pendente; nao e, o nome ja foi batido.</t>
   </si>
   <si>
+    <t xml:space="preserve">O resto da troca de nome PAXTER para PADAXOR, agora dentro das telas. O titulo da aba ja foi feito no item 15.</t>
+  </si>
+  <si>
     <t xml:space="preserve">RESUMO</t>
   </si>
   <si>
@@ -1028,6 +1147,534 @@
   </si>
   <si>
     <t xml:space="preserve">acrescente aqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PADAXOR — Glossario para o Dr. Caio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toda palavra tecnica usada pela equipe entra aqui. Ordem alfabetica automatica. Palavra nova aparece numa conversa, vira linha nova aqui.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palavra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinonimos e como aparece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em linguagem de leigo, com analogia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interface, endpoint, rota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interface de Programacao de Aplicacoes. O conjunto de portas por onde um programa pede coisas a outro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o balcao de atendimento de um laboratorio. Voce nao entra no laboratorio: chega no balcao, entrega o pedido, recebe o resultado. A API e o balcao, e cada guiche e uma rota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O site conversa com o servidor por API. Quando o site mostra a lista de clientes, ele pediu pela API.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">append-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">so cresce, log append-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registro em que se acrescenta linha, nunca se apaga nem se corrige linha antiga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o prontuario do paciente. Voce nao apaga a evolucao de ontem: escreve a de hoje embaixo. Se errou ontem, escreve hoje que errou. O erro fica registrado, e e isso que da valor legal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A aba HISTORICO desta planilha e append-only. E o que permite comparar o que foi pedido com o que foi feito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copia de seguranca, dump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copia dos dados guardada separada do original, para restaurar se o original se perder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o seguro do carro. Custa todo mes e parece dinheiro jogado fora, ate o dia da batida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 2 da fila. Salvou a carga do banco quando o primeiro apagamento travou no meio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">banco de dados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">banco, base, Postgres, SQL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa que guarda os dados de forma organizada e permite buscar rapido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o arquivo de fichas da clinica, mas que responde em um centesimo de segundo e nunca perde uma ficha por descuido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seus 3.683 clientes e 24.287 resultados de exame vivem num banco chamado PostgreSQL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ramificacao, ramo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copia paralela do codigo onde se trabalha sem mexer na versao que esta no ar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a via de um exame: voce faz o rascunho da conduta numa folha separada antes de escrever no prontuario oficial. Se der errado, joga a folha fora e o prontuario continua intacto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo trabalho meu comeca numa ramificacao. So vai para o codigo oficial depois de conferido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integracao continua, GitHub Actions, esteira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robo que roda os testes sozinho a cada mudanca e barra o que quebrou antes de publicar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a conferencia dupla da enfermagem antes de aplicar a medicacao. Ninguem confia so na memoria de quem preparou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 32 da fila. Hoje nao existe nenhum: por isso os erros das ultimas horas so apareceram depois de publicados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apontamento de DNS, ALIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de registro de endereco na internet que diz 'este nome aponta para aquele outro nome'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o encaminhamento de telefone: quem liga para o numero antigo cai automaticamente no novo, sem saber que foi encaminhado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 13. O Registro.br nao faz um tipo especifico que o servidor precisa; o Cloudflare faz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gravacao, ponto de salvamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um pacote de mudancas no codigo, com autor, data e explicacao, gravado de forma permanente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E uma entrada assinada no prontuario: quem escreveu, quando, e o que mudou. Nao se apaga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Dr. Replit entregou os itens 11 e 15 no commit 3a38349. Esse numero e a prova de que existe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lista de origens permitidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regra que diz quais sites tem permissao de chamar o seu servidor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a lista da portaria do predio: so sobe quem esta na lista. Sem a lista certa, ate o morador fica na calcada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 3. Estava com valor invalido e por isso o site nao conseguia falar com o servidor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deploy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">publicar, subir, colocar no ar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levar o codigo do computador do programador para o servidor onde o cliente usa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a diferenca entre escrever a receita no bloco e entregar na mao do paciente. Enquanto nao entregou, nao existe para ele.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regra numero 1 da equipe: ninguem anuncia pronto antes de estar publicado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DKIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assinatura de e-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assinatura digital que prova que o e-mail saiu mesmo do dominio que diz ter saido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o carimbo e a assinatura no receituario. Sem eles, a farmacia trata como falsificacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 29. Sem isso o Gmail marca seu convite de socio com tarja vermelha de golpe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">servidor de nomes, dominio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema que traduz um nome como padaxor.com.br no endereco numerico real do servidor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a lista telefonica: voce sabe o nome da pessoa, e ela devolve o numero. Ninguem decora o numero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itens 13 e 14. Sem DNS certo, o endereco padaxor.com.br nao chega no sistema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rota, porta, guiche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um endereco especifico da API que faz uma coisa so.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o guiche especifico dentro do balcao: um guiche para entregar exame, outro para retirar resultado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/api/collaborator/login e o guiche de entrada do colaborador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chave estrangeira, foreign key, vinculo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coluna que amarra uma linha de uma tabela a uma linha de outra tabela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o numero do prontuario escrito no pedido de exame: e o que amarra aquele exame aquele paciente e nao a outro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 8. Hoje o colaborador nao tem esse vinculo com a clinica: existe solto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resumo criptografico, impressao digital, identificador de commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero unico calculado a partir de um conteudo. Mudou uma virgula no conteudo, o numero muda inteiro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a impressao digital de um documento. Duas pessoas nao tem a mesma, e a sua nao muda sozinha. Se o documento foi adulterado, a impressao digital nao bate mais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serve para provar entrega. Quando eu digo 'commit 3a38349', voce pode conferir que aquele codigo existe exatamente daquele jeito. E a regra anti-fantasia do seu Art. 19.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idempotente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reprocessavel, seguro para repetir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operacao que pode ser repetida quantas vezes for e o resultado final e sempre o mesmo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E apertar o botao do elevador. Apertar dez vezes nao chama dez elevadores: o andar continua marcado uma vez so.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 57 da sua Biblia. Toda operacao que grava dado tem de poder rodar de novo sem duplicar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indice unico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique index, restricao de unicidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regra do banco que impede dois registros de terem o mesmo valor num campo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o CPF: o cartorio nao deixa dois cadastros com o mesmo numero. A regra vive no cartorio, nao na boa vontade de quem preenche.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 17. Impede dois colaboradores com o mesmo nome de usuario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">principal, tronco, producao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A ramificacao oficial do codigo, a que esta valendo de verdade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o prontuario oficial, nao o rascunho. O que nao esta nele, oficialmente nao aconteceu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regra da equipe: construido no ambiente local e rascunho; so vale quando esta na main.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">merge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesclar, juntar, fundir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juntar o trabalho de duas ramificacoes num so.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E juntar as anotacoes de dois medicos sobre o mesmo paciente num prontuario unico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O perigo e o conflito: quando os dois mexeram na mesma linha e o programa nao sabe qual vale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">middleware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">camada intermediaria, porteiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codigo que fica no meio do caminho de toda chamada e decide se ela passa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o porteiro do predio: toda visita passa por ele antes de chegar no apartamento, e ele decide quem sobe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O basicAuth e o porteiro do sistema. Foi um dos tres arquivos onde dois agentes colidiram.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">migracao, alteracao de estrutura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Script que muda a estrutura do banco de dados de forma controlada e registrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a reforma da clinica com planta aprovada e registrada, em vez de derrubar parede no impulso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O item 8 vai precisar de uma: acrescentar a coluna de vinculo da clinica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">simulacao, dado de mentira, placeholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado ou resposta falsa usada so para testar, no lugar do dado real.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o manequim de treinamento. Serve para ensaiar, e e perigoso se alguem esquecer e tratar como paciente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuidado permanente: mock esquecido em producao vira numero falso na tela do cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multi-tenant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multi-inquilino, isolamento entre clinicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um mesmo sistema atendendo varios clientes com os dados separados entre si.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E um predio de consultorios: mesma estrutura, mesmo elevador, mas cada sala tem chave propria e ninguem entra na do outro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itens 9 e 37. E o que precisa estar de pe antes de licenciar a segunda clinica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pull request, pedido de incorporacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido formal para juntar um trabalho na versao oficial, com espaco para revisao antes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o pedido de parecer antes da cirurgia. Alguem olha, comenta, e so depois entra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A PR numero 6 e onde vive esta planilha e a fila de producao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aplicativo web progressivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site que se comporta como aplicativo de celular, com icone na tela inicial e uso sem internet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E um aparelho que serve de dois jeitos: no consultorio parece bancada, na mao vira portatil. Mesmo aparelho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideia para a area do paciente no celular, sem publicar em loja de aplicativos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">controle de acesso por papel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regra que define o que cada tipo de usuario pode ver e fazer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a diferenca entre medico, enfermeiro e recepcao no sistema da clinica: cada um ve a tela do seu papel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precisa existir para o licenciado ver so a propria clinica e voce ver todas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repositorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repo, GitHub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O lugar onde o codigo mora, com todo o historico de quem mudou o que e quando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o arquivo morto da clinica, mas em que nada se perde e da para voltar a qualquer dia do passado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protocolo-Manager e Parlegis sao dois repositorios diferentes, de dois sistemas diferentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row-Level Security, seguranca por linha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trava dentro do proprio banco que impede um cliente de ler a linha de outro, mesmo com erro do programador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a tranca da porta da sala, nao o aviso 'por favor nao entre'. O aviso depende da boa vontade; a tranca nao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 9, o mais critico da fila. Hoje existem zero trancas: a separacao depende do programador lembrar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scrypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">algoritmo de senha, derivacao de chave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metodo de embaralhar a senha de um jeito que nao se desfaz, para guardar sem saber qual e.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E guardar a impressao digital do paciente em vez do dedo dele. Da para conferir se bate, mas ninguem reconstroi o dedo a partir dela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 10. Existem dois usos diferentes com a mesma etiqueta, e foi isso que quebrou seu login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autorizacao de remetente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registro que diz quais servidores tem permissao de mandar e-mail em nome do seu dominio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a lista de quem pode assinar receita em nome da clinica. Sem ela, qualquer um assina.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 29, junto com o DKIM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eventos do servidor, tempo real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnica em que o servidor avisa a tela sozinho quando algo muda, sem a tela ficar perguntando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o monitor de sinais vitais: ele avisa quando muda, voce nao fica olhando de minuto em minuto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideia para o painel de consumo atualizar sozinho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cracha, Bearer, chave de sessao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codigo temporario que prova quem voce e depois que voce ja fez o login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E a pulseira do hospital. Voce se identifica uma vez na recepcao e depois so mostra a pulseira em cada setor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 5. O cracha existia, mas o porteiro nao olhava para ele.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPSERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inserir ou atualizar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operacao que grava o registro se ele nao existe, e atualiza se ja existe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E abrir ficha se o paciente e novo, ou atualizar a que ja existe se ele ja veio antes. Uma decisao so, automatica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serve para carga de dados poder rodar duas vezes sem duplicar ninguem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">webhook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aviso automatico, gancho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamada que um sistema faz no outro sozinho quando um evento acontece.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E o laboratorio que liga para voce quando o resultado critico sai, em vez de voce ligar de hora em hora perguntando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item 28: o provisionamento da clinica deve pendurar no aviso de pagamento confirmado, nunca antes dele.</t>
   </si>
 </sst>
 </file>
@@ -1421,6 +2068,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -1601,7 +2252,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1613,6 +2264,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1627,6 +2279,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -1640,6 +2293,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -1669,1117 +2323,1234 @@
       <c r="I4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>29</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>34</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="G14" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>71</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>77</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>82</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>88</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>93</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>98</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="G22" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>113</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>123</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="F27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="H27" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>131</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>137</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>147</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>151</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>161</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>171</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>176</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="n">
         <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>181</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>185</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="n">
         <v>35</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>189</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>194</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="n">
         <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>198</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
         <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>164</v>
+        <v>202</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="7" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="8" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="C45" s="9" t="n">
         <f aca="false">COUNTIF(F5:F42,"CONCLUIDO")</f>
@@ -2788,7 +3559,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="8" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="C46" s="9" t="n">
         <f aca="false">COUNTIF(F5:F42,"A FAZER")</f>
@@ -2797,7 +3568,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="8" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="C47" s="9" t="n">
         <f aca="false">COUNTIF(F5:F42,"AGUARDANDO")</f>
@@ -2806,7 +3577,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="8" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="C48" s="9" t="n">
         <f aca="false">COUNTA(A5:A42)</f>
@@ -2814,10 +3585,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I42"/>
+  <autoFilter ref="A4:J42"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F42" type="list">
@@ -2856,7 +3627,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2865,7 +3636,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2874,114 +3645,114 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2990,7 +3761,7 @@
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2999,7 +3770,7 @@
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3008,7 +3779,7 @@
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3017,7 +3788,7 @@
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3061,7 +3832,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3070,7 +3841,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3082,16 +3853,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3099,13 +3870,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -3114,13 +3885,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -3129,13 +3900,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E7" s="12"/>
     </row>
@@ -3144,13 +3915,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E8" s="12"/>
     </row>
@@ -3159,13 +3930,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -3174,13 +3945,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -3189,13 +3960,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -3204,13 +3975,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -3219,13 +3990,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -3234,36 +4005,36 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3295,78 +4066,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>244</v>
+        <v>283</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>245</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>249</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>257</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -3399,7 +4170,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3407,7 +4178,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>259</v>
+        <v>298</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3415,128 +4186,128 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>271</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>278</v>
+        <v>317</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>284</v>
+        <v>323</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>295</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3573,7 +4344,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3585,7 +4356,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3597,293 +4368,293 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>301</v>
+        <v>340</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>322</v>
+        <v>361</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>326</v>
+        <v>365</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -3908,4 +4679,658 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E38"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">GLOSSARIO!$A$4:$E$38</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$14</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$17</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="557">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -528,13 +528,16 @@
     <t xml:space="preserve">Declarar servicos, comandos e caminhos no repositorio.</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Manus</t>
+  </si>
+  <si>
     <t xml:space="preserve">P3 baixo</t>
   </si>
   <si>
-    <t xml:space="preserve">Hoje a configuracao vive so no painel. Se o projeto sumir, o codigo nao reconstroi o sistema.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escrever no proprio codigo como o sistema e montado. Hoje isso so existe dentro do painel de um fornecedor: se a conta sumir, o codigo sozinho nao remonta o sistema.</t>
+    <t xml:space="preserve">Passou para o Dr. Manus em 30/07: missao de escopo fechado, ponta a ponta, sem dependencia. Libera o Dr. Code para os tres itens P0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escrever no proprio codigo como o sistema e montado. Hoje isso so existe dentro do painel de um fornecedor: se a conta sumir, o codigo sozinho nao remonta o sistema. Passou para o Dr. Manus, que faz missao inteira sozinho.</t>
   </si>
   <si>
     <t xml:space="preserve">Colapsar o Supabase</t>
@@ -609,16 +612,13 @@
     <t xml:space="preserve">Missao a definir para o Dr. Manus</t>
   </si>
   <si>
-    <t xml:space="preserve">Ainda sem frente atribuida nesta fase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Manus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfil: executa missao inteira de ponta a ponta. Candidato natural: item 32 ou 33.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaga aberta para o Dr. Manus, que executa missao inteira sozinho. Ainda sem frente definida nesta fase.</t>
+    <t xml:space="preserve">Vaga usada em 30/07: o Dr. Manus assumiu o item 30. Esta linha fica como registro, nao se apaga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fechada em 30/07 com a entrada dele no item 30. Proxima missao entra como numero novo, nunca reaproveitando este.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Era a vaga aberta do Dr. Manus. Ele entrou em 30/07 e pegou o item 30, entao a vaga fechou. A linha fica como registro: nada se apaga.</t>
   </si>
   <si>
     <t xml:space="preserve">Auditoria de rotas: consulta sem filtro de empresa</t>
@@ -741,7 +741,7 @@
     <t xml:space="preserve">Producao sem combinar antes</t>
   </si>
   <si>
-    <t xml:space="preserve">Sem frente nesta fase. Candidato: suite de testes (32) ou renomeacao (33)</t>
+    <t xml:space="preserve">railway.toml versionado (30). Proximo candidato: X-Request-Id e contrato da API (35)</t>
   </si>
   <si>
     <t xml:space="preserve">REGRA DE CONVIVENCIA</t>
@@ -1132,6 +1132,33 @@
   </si>
   <si>
     <t xml:space="preserve">Item novo: resto do rebrand nas telas internas, que o item 15 comecou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Dr. Manus entrou na equipe de fato. Item de escopo fechado, ponta a ponta, sem dependencia — perfil dele. Libera o Dr. Code para os tres itens P0 de isolamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pedido do CEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A vaga em aberto do Dr. Manus foi usada: ele assumiu o item 30. A linha fica como registro; proxima missao dele entra como numero novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coordenacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recado no repositorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recado no Slack em tempo real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premissa minha estava errada: eu afirmei que os agentes nao conseguiam conversar entre si. Todos tinham conector de Slack. Canal #padaxor-projeto passa a ser a caixa de recados, e o CEO sai do meio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARTILHA/06 em PADUA-SOFTWARE-DESIGN</t>
   </si>
   <si>
     <t xml:space="preserve">estrutura</t>
@@ -3266,7 +3293,7 @@
         <v>164</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>15</v>
@@ -3275,16 +3302,16 @@
         <v>53</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>97</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3292,31 +3319,31 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>97</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3324,10 +3351,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>28</v>
@@ -3339,16 +3366,16 @@
         <v>53</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3356,31 +3383,31 @@
         <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>60</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3388,10 +3415,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>23</v>
@@ -3403,16 +3430,16 @@
         <v>53</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>112</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3420,10 +3447,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>28</v>
@@ -3435,47 +3462,47 @@
         <v>53</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>60</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="D40" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H40" s="6" t="s">
+      <c r="F40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H40" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="4" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3554,7 +3581,7 @@
       </c>
       <c r="C45" s="9" t="n">
         <f aca="false">COUNTIF(F5:F42,"CONCLUIDO")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3572,7 +3599,7 @@
       </c>
       <c r="C47" s="9" t="n">
         <f aca="false">COUNTIF(F5:F42,"AGUARDANDO")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3730,7 +3757,7 @@
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>233</v>
@@ -4330,7 +4357,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -4634,38 +4661,116 @@
         <v>28</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H14"/>
+  <autoFilter ref="A4:H17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -4698,7 +4803,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4707,7 +4812,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4716,16 +4821,16 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>281</v>
@@ -4733,585 +4838,585 @@
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>

--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">GLOSSARIO!$A$4:$E$38</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$17</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$19</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="575">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -744,6 +744,42 @@
     <t xml:space="preserve">railway.toml versionado (30). Proximo candidato: X-Request-Id e contrato da API (35)</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peca avulsa e auditoria independente: logo, mockup, imagem, grafico, rascunho de texto, e segunda opiniao sobre spec e codigo de outro agente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAO commita nada. Entrega arquivo na doca; quem commita e o dono do territorio. Nao decide arquitetura nem mexe em fila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem item proprio ainda. Auditoria independente e sob demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAGA 1 — a definir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a definir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A definir no ritual de entrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tudo, ate a matriz ser preenchida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livre. Ver o ritual de entrada no capitulo 07 da cartilha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAGA 2 — a definir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAGA 3 — a definir</t>
+  </si>
+  <si>
     <t xml:space="preserve">REGRA DE CONVIVENCIA</t>
   </si>
   <si>
@@ -1159,6 +1195,24 @@
   </si>
   <si>
     <t xml:space="preserve">CARTILHA/06 em PADUA-SOFTWARE-DESIGN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 membros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 membros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Chat (ChatGPT) entrou no quadro por decisao do CEO. Territorio escolhido para NAO sobrepor ninguem: peca avulsa e auditoria independente, entregue na doca, sem commitar. Modelo de familia diferente lendo a mesma spec pega o que o autor nao viu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 membros e 3 vagas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tres vagas abertas para agente futuro, com rotulo VAGA e nao em branco: o espelho le a matriz varrendo ate a celula vazia, e linha em branco cortaria tudo abaixo. Preenchimento so pelo ritual de entrada.</t>
   </si>
   <si>
     <t xml:space="preserve">estrutura</t>
@@ -3643,7 +3697,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="22"/>
@@ -3772,65 +3826,133 @@
         <v>236</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+    <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
     </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3859,7 +3981,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3868,7 +3990,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3880,16 +4002,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3897,13 +4019,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -3912,13 +4034,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -3927,10 +4049,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>122</v>
@@ -3942,10 +4064,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>122</v>
@@ -3957,13 +4079,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -3972,13 +4094,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -3987,13 +4109,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -4002,13 +4124,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -4017,13 +4139,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -4032,36 +4154,36 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4093,78 +4215,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -4197,7 +4319,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4205,7 +4327,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4213,128 +4335,128 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -4357,7 +4479,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -4371,7 +4493,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4383,7 +4505,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4395,33 +4517,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>28</v>
@@ -4430,30 +4552,30 @@
         <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
@@ -4465,15 +4587,15 @@
         <v>53</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>28</v>
@@ -4491,21 +4613,21 @@
         <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
@@ -4517,15 +4639,15 @@
         <v>87</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -4543,21 +4665,21 @@
         <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>7</v>
@@ -4569,21 +4691,21 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
@@ -4595,24 +4717,24 @@
         <v>53</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>15</v>
@@ -4621,24 +4743,24 @@
         <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>15</v>
@@ -4647,15 +4769,15 @@
         <v>53</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>28</v>
@@ -4673,21 +4795,21 @@
         <v>165</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>7</v>
@@ -4699,15 +4821,15 @@
         <v>16</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>28</v>
@@ -4716,24 +4838,24 @@
         <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>28</v>
@@ -4742,35 +4864,87 @@
         <v>15</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
+    </row>
+    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H17"/>
+  <autoFilter ref="A4:H19"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -4803,7 +4977,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4812,7 +4986,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4821,602 +4995,602 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>

--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">GLOSSARIO!$A$4:$E$38</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$19</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$42</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$21</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="587">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -633,6 +633,18 @@
     <t xml:space="preserve">Varrer todas as portas do sistema procurando as que leem dados sem perguntar de qual clinica. A entrega e a LISTA dos buracos, nao o conserto. E o exame antes da cirurgia: sem a lista, o item 9 seria operado as cegas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Espelho dos .md no cofre do Dr. Obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escrever os .md da equipe numa pasta do Google Drive que o Obsidian sincroniza. Sem conector novo: o Drive ja esta ligado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Art. 23-B da Biblia manda todo guia e licao aprendida terminar no cofre. Hoje nada chega la: cartilha, colisao e espelho estao so no GitHub.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fazer os documentos da equipe caírem tambem na sua pasta do Obsidian, o seu segundo cerebro. Hoje eles existem so no GitHub, que voce nao abre para consultar. E a sua propria regra que nao esta sendo cumprida.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marca PAXTER para PADAXOR nas telas internas</t>
   </si>
   <si>
@@ -1207,6 +1219,30 @@
   </si>
   <si>
     <t xml:space="preserve">Dr. Chat (ChatGPT) entrou no quadro por decisao do CEO. Territorio escolhido para NAO sobrepor ninguem: peca avulsa e auditoria independente, entregue na doca, sem commitar. Modelo de familia diferente lendo a mesma spec pega o que o autor nao viu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sem Cloudflare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudflare ligado, sem DNS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERRO MEU: recomendei o conector Cloudflare para resolver o DNS dos itens 13, 14, 27 e 29. Conferi a lista de ferramentas DEPOIS de o CEO instalar: o conector expoe R2, D1, KV, Workers, Hyperdrive e busca em documentacao. ZERO ferramentas de DNS. Os quatro itens continuam travados e nada mudou de estado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARTILHA/08 em PADUA-SOFTWARE-DESIGN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item novo: o Art. 23-B da Biblia nao esta sendo cumprido. Nenhum .md escrito nesta madrugada chegou ao cofre do Dr. Obsidian. Conserto usa o Google Drive, que ja esta ligado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">achado durante a revisao de conectores</t>
   </si>
   <si>
     <t xml:space="preserve">6 membros e 3 vagas</t>
@@ -2333,7 +2369,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3594,7 +3630,7 @@
     </row>
     <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>200</v>
@@ -3603,7 +3639,7 @@
         <v>201</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>15</v>
@@ -3612,7 +3648,7 @@
         <v>53</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>65</v>
@@ -3624,59 +3660,91 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="7" t="s">
+    <row r="43" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>204</v>
       </c>
+      <c r="C43" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="C45" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F42,"CONCLUIDO")</f>
-        <v>10</v>
+      <c r="B45" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C46" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F42,"A FAZER")</f>
-        <v>17</v>
+        <f aca="false">COUNTIF(F5:F43,"CONCLUIDO")</f>
+        <v>10</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C47" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F42,"AGUARDANDO")</f>
-        <v>11</v>
+        <f aca="false">COUNTIF(F5:F43,"A FAZER")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="8" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C48" s="9" t="n">
-        <f aca="false">COUNTA(A5:A42)</f>
-        <v>38</v>
+        <f aca="false">COUNTIF(F5:F43,"AGUARDANDO")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <f aca="false">COUNTA(A5:A43)</f>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J42"/>
+  <autoFilter ref="A4:J43"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F42" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F43" type="list">
       <formula1>"A FAZER,EM CURSO,AGUARDANDO,CONCLUIDO,CANCELADO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G42" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G43" type="list">
       <formula1>"P0 critico,P1 alto,P2 medio,P3 baixo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3708,7 +3776,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3717,7 +3785,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3726,19 +3794,19 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3746,16 +3814,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3763,33 +3831,33 @@
         <v>28</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3797,16 +3865,16 @@
         <v>43</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3814,94 +3882,94 @@
         <v>165</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>243</v>
-      </c>
       <c r="C12" s="10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3910,7 +3978,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3919,7 +3987,7 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3928,7 +3996,7 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3937,7 +4005,7 @@
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3981,7 +4049,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3990,7 +4058,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4002,16 +4070,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4019,13 +4087,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -4034,13 +4102,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -4049,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>122</v>
@@ -4064,10 +4132,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>122</v>
@@ -4079,13 +4147,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -4094,13 +4162,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -4109,13 +4177,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -4124,13 +4192,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -4139,13 +4207,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -4154,36 +4222,36 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -4215,78 +4283,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4319,7 +4387,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4327,7 +4395,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4335,128 +4403,128 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4479,7 +4547,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -4493,7 +4561,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4505,7 +4573,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4517,33 +4585,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>28</v>
@@ -4552,30 +4620,30 @@
         <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
@@ -4587,15 +4655,15 @@
         <v>53</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>28</v>
@@ -4613,21 +4681,21 @@
         <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
@@ -4639,15 +4707,15 @@
         <v>87</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -4665,21 +4733,21 @@
         <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>7</v>
@@ -4691,21 +4759,21 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
@@ -4717,24 +4785,24 @@
         <v>53</v>
       </c>
       <c r="G11" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>373</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>15</v>
@@ -4743,24 +4811,24 @@
         <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>15</v>
@@ -4769,15 +4837,15 @@
         <v>53</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>28</v>
@@ -4795,21 +4863,21 @@
         <v>165</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>7</v>
@@ -4821,15 +4889,15 @@
         <v>16</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>28</v>
@@ -4838,24 +4906,24 @@
         <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>28</v>
@@ -4864,24 +4932,24 @@
         <v>15</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>28</v>
@@ -4890,61 +4958,113 @@
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="F19" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>398</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
+      <c r="F20" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H19"/>
+  <autoFilter ref="A4:H21"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -4977,7 +5097,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4986,7 +5106,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4995,602 +5115,602 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>

--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">GLOSSARIO!$A$4:$E$38</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$21</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$43</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$44</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="593">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -633,6 +633,18 @@
     <t xml:space="preserve">Varrer todas as portas do sistema procurando as que leem dados sem perguntar de qual clinica. A entrega e a LISTA dos buracos, nao o conserto. E o exame antes da cirurgia: sem a lista, o item 9 seria operado as cegas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Armazenamento R2 na mesma rota de exames do Drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A rota que hoje grava exame no Google Drive passa a gravar TAMBEM no R2 do Cloudflare, com nome padronizado: cliente-&lt;id&gt;/&lt;data&gt;/&lt;tipo&gt;.pdf. Espelho, nao troca: o Drive continua funcionando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIMEIRO DA FILA DE EXECUCAO por decisao do CEO em 30/07. Motivo declarado por ele: acompanhar uma construcao inteira passando pela ferramenta de coordenacao, enquanto aprende. Nao e P0 porque P0 nesta fila significa dano irreversivel, e aqui nada se perde.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoje o exame do cliente e guardado no Google Drive. Isso faz o sistema guardar TAMBEM num deposito de arquivos mais barato, com o nome ja saindo organizado na gravacao. O Drive continua igual: e espelho, nao troca. Serve para voce ver um item nascer, andar e fechar usando a nossa propria ferramenta.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Espelho dos .md no cofre do Dr. Obsidian</t>
   </si>
   <si>
@@ -1219,6 +1231,12 @@
   </si>
   <si>
     <t xml:space="preserve">Dr. Chat (ChatGPT) entrou no quadro por decisao do CEO. Territorio escolhido para NAO sobrepor ninguem: peca avulsa e auditoria independente, entregue na doca, sem commitar. Modelo de familia diferente lendo a mesma spec pega o que o autor nao viu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item novo pedido pelo CEO, e ele mesmo declarou que nao e urgente: quer acompanhar uma construcao inteira passando pela ferramenta de coordenacao enquanto aprende. Fica primeiro na fila de execucao, com prioridade P1 e nao P0 — P0 aqui significa dano irreversivel, e este item nao perde nada.</t>
   </si>
   <si>
     <t xml:space="preserve">conector</t>
@@ -2369,7 +2387,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3630,7 +3648,7 @@
     </row>
     <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>200</v>
@@ -3639,7 +3657,7 @@
         <v>201</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>15</v>
@@ -3648,10 +3666,10 @@
         <v>53</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>202</v>
@@ -3662,7 +3680,7 @@
     </row>
     <row r="43" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>204</v>
@@ -3671,7 +3689,7 @@
         <v>205</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>15</v>
@@ -3680,7 +3698,7 @@
         <v>53</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>65</v>
@@ -3692,59 +3710,91 @@
         <v>207</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="7" t="s">
+    <row r="44" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>208</v>
       </c>
+      <c r="C44" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C46" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F43,"CONCLUIDO")</f>
-        <v>10</v>
+      <c r="B46" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C47" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F43,"A FAZER")</f>
-        <v>18</v>
+        <f aca="false">COUNTIF(F5:F44,"CONCLUIDO")</f>
+        <v>10</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C48" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F43,"AGUARDANDO")</f>
-        <v>11</v>
+        <f aca="false">COUNTIF(F5:F44,"A FAZER")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C49" s="9" t="n">
-        <f aca="false">COUNTA(A5:A43)</f>
-        <v>39</v>
+        <f aca="false">COUNTIF(F5:F44,"AGUARDANDO")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <f aca="false">COUNTA(A5:A44)</f>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J43"/>
+  <autoFilter ref="A4:J44"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F43" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F44" type="list">
       <formula1>"A FAZER,EM CURSO,AGUARDANDO,CONCLUIDO,CANCELADO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G43" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G44" type="list">
       <formula1>"P0 critico,P1 alto,P2 medio,P3 baixo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3776,7 +3826,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3785,7 +3835,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3794,19 +3844,19 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3814,16 +3864,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3831,33 +3881,33 @@
         <v>28</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3865,16 +3915,16 @@
         <v>43</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3882,94 +3932,94 @@
         <v>165</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>247</v>
-      </c>
       <c r="C12" s="10" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3978,7 +4028,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3987,7 +4037,7 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3996,7 +4046,7 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4005,7 +4055,7 @@
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4049,7 +4099,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4058,7 +4108,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4070,16 +4120,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4087,13 +4137,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -4102,13 +4152,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -4117,10 +4167,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>122</v>
@@ -4132,10 +4182,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>122</v>
@@ -4147,13 +4197,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -4162,13 +4212,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -4177,13 +4227,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -4192,13 +4242,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -4207,13 +4257,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -4222,36 +4272,36 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -4283,78 +4333,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4387,7 +4437,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4395,7 +4445,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4403,128 +4453,128 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -4547,7 +4597,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -4561,7 +4611,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4573,7 +4623,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4585,33 +4635,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>28</v>
@@ -4620,30 +4670,30 @@
         <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
@@ -4655,15 +4705,15 @@
         <v>53</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>28</v>
@@ -4681,21 +4731,21 @@
         <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
@@ -4707,15 +4757,15 @@
         <v>87</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -4733,21 +4783,21 @@
         <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>7</v>
@@ -4759,21 +4809,21 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
@@ -4785,24 +4835,24 @@
         <v>53</v>
       </c>
       <c r="G11" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>15</v>
@@ -4811,24 +4861,24 @@
         <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>15</v>
@@ -4837,15 +4887,15 @@
         <v>53</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>28</v>
@@ -4863,21 +4913,21 @@
         <v>165</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>7</v>
@@ -4889,15 +4939,15 @@
         <v>16</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>28</v>
@@ -4906,24 +4956,24 @@
         <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>28</v>
@@ -4932,102 +4982,102 @@
         <v>15</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>397</v>
-      </c>
       <c r="F18" s="5" t="s">
-        <v>398</v>
+        <v>53</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>401</v>
+        <v>15</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>15</v>
+        <v>403</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>53</v>
+        <v>404</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>394</v>
-      </c>
       <c r="F20" s="5" t="s">
-        <v>404</v>
+        <v>53</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>28</v>
@@ -5036,35 +5086,61 @@
         <v>15</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H21"/>
+  <autoFilter ref="A4:H22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -5097,7 +5173,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5106,7 +5182,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5115,602 +5191,602 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>

--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">GLOSSARIO!$A$4:$E$38</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$44</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$24</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$45</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="602">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -639,12 +639,24 @@
     <t xml:space="preserve">A rota que hoje grava exame no Google Drive passa a gravar TAMBEM no R2 do Cloudflare, com nome padronizado: cliente-&lt;id&gt;/&lt;data&gt;/&lt;tipo&gt;.pdf. Espelho, nao troca: o Drive continua funcionando.</t>
   </si>
   <si>
-    <t xml:space="preserve">PRIMEIRO DA FILA DE EXECUCAO por decisao do CEO em 30/07. Motivo declarado por ele: acompanhar uma construcao inteira passando pela ferramenta de coordenacao, enquanto aprende. Nao e P0 porque P0 nesta fila significa dano irreversivel, e aqui nada se perde.</t>
+    <t xml:space="preserve">Entregue 30/07 no commit f21e2eb: lib/examR2Storage.ts com dry-run (Art. 58), idempotencia (Art. 57) e best-effort — falha no cofre nao derruba o Drive. Sem credencial R2 no ambiente: usa o cofre de objetos ja existente como segundo destino, trocar provedor e uma linha. NAO criou terceiro armazenamento. PRIMEIRO DA FILA DE EXECUCAO por decisao do CEO em 30/07. Motivo declarado por ele: acompanhar uma construcao inteira passando pela ferramenta de coordenacao, enquanto aprende. Nao e P0 porque P0 nesta fila significa dano irreversivel, e aqui nada se perde.</t>
   </si>
   <si>
     <t xml:space="preserve">Hoje o exame do cliente e guardado no Google Drive. Isso faz o sistema guardar TAMBEM num deposito de arquivos mais barato, com o nome ja saindo organizado na gravacao. O Drive continua igual: e espelho, nao troca. Serve para voce ver um item nascer, andar e fechar usando a nossa propria ferramenta.</t>
   </si>
   <si>
+    <t xml:space="preserve">Rota de upload na area do paciente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST para o paciente enviar arquivo. Cai na subpasta EXAMES da pasta dele e entra no mesmo motor de extracao do drive-watcher.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoje NAO EXISTE: seis rotas de escrita na area do paciente e nenhuma de upload. O paciente so le. Conferido rota por rota em area-paciente.ts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoje o paciente consegue VER os exames dele na area do cliente, mas nao consegue MANDAR nenhum. Falta a porta de entrada. Isso cria essa porta, e o arquivo que ele manda cai no mesmo motor que ja le exame automaticamente.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Espelho dos .md no cofre do Dr. Obsidian</t>
   </si>
   <si>
@@ -1234,6 +1246,21 @@
   </si>
   <si>
     <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregou em 7 minutos e melhor do que a minha correcao: espelhou no cofre de objetos que JA existia em vez de criar um terceiro, citou Art. 57 e 58 pelo nome, deixou best-effort para nao derrubar o Drive, e declarou honestamente que nao ha credencial R2 no ambiente. Seguiu o protocolo: mudou o estado citando o hash.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit f21e2eb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achado ao conferir o codigo: a area do paciente tem seis rotas de escrita e NENHUMA de upload. O paciente nao consegue enviar arquivo hoje. O CEO supunha que conseguia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">artifacts/api-server/src/routes/area-paciente.ts</t>
   </si>
   <si>
     <t xml:space="preserve">Item novo pedido pelo CEO, e ele mesmo declarou que nao e urgente: quer acompanhar uma construcao inteira passando pela ferramenta de coordenacao enquanto aprende. Fica primeiro na fila de execucao, com prioridade P1 e nao P0 — P0 aqui significa dano irreversivel, e este item nao perde nada.</t>
@@ -2387,7 +2414,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3647,40 +3674,40 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G42" s="5" t="s">
+      <c r="F42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H42" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I42" s="5" t="s">
+      <c r="H42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="4" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>204</v>
@@ -3689,7 +3716,7 @@
         <v>205</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>15</v>
@@ -3698,10 +3725,10 @@
         <v>53</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>206</v>
@@ -3712,7 +3739,7 @@
     </row>
     <row r="44" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>208</v>
@@ -3721,7 +3748,7 @@
         <v>209</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>15</v>
@@ -3730,7 +3757,7 @@
         <v>53</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>65</v>
@@ -3742,59 +3769,91 @@
         <v>211</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="7" t="s">
+    <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>212</v>
       </c>
+      <c r="C45" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C47" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F44,"CONCLUIDO")</f>
-        <v>10</v>
+      <c r="B47" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C48" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F44,"A FAZER")</f>
-        <v>19</v>
+        <f aca="false">COUNTIF(F5:F45,"CONCLUIDO")</f>
+        <v>11</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C49" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F44,"AGUARDANDO")</f>
-        <v>11</v>
+        <f aca="false">COUNTIF(F5:F45,"A FAZER")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C50" s="9" t="n">
-        <f aca="false">COUNTA(A5:A44)</f>
-        <v>40</v>
+        <f aca="false">COUNTIF(F5:F45,"AGUARDANDO")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <f aca="false">COUNTA(A5:A45)</f>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J44"/>
+  <autoFilter ref="A4:J45"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F44" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F45" type="list">
       <formula1>"A FAZER,EM CURSO,AGUARDANDO,CONCLUIDO,CANCELADO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G44" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G45" type="list">
       <formula1>"P0 critico,P1 alto,P2 medio,P3 baixo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3826,7 +3885,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3835,7 +3894,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3844,19 +3903,19 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3864,16 +3923,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3881,33 +3940,33 @@
         <v>28</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3915,16 +3974,16 @@
         <v>43</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3932,94 +3991,94 @@
         <v>165</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>251</v>
-      </c>
       <c r="C12" s="10" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>252</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4028,7 +4087,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4037,7 +4096,7 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4046,7 +4105,7 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4055,7 +4114,7 @@
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4099,7 +4158,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4108,7 +4167,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4120,16 +4179,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4137,13 +4196,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -4152,13 +4211,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -4167,10 +4226,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>122</v>
@@ -4182,10 +4241,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>122</v>
@@ -4197,13 +4256,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -4212,13 +4271,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -4227,13 +4286,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -4242,13 +4301,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -4257,13 +4316,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -4272,36 +4331,36 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -4333,78 +4392,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4437,7 +4496,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4445,7 +4504,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4453,128 +4512,128 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -4597,7 +4656,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -4611,7 +4670,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4623,7 +4682,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4635,33 +4694,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>28</v>
@@ -4670,30 +4729,30 @@
         <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
@@ -4705,15 +4764,15 @@
         <v>53</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>28</v>
@@ -4731,21 +4790,21 @@
         <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
@@ -4757,15 +4816,15 @@
         <v>87</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -4783,21 +4842,21 @@
         <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>7</v>
@@ -4809,21 +4868,21 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
@@ -4835,24 +4894,24 @@
         <v>53</v>
       </c>
       <c r="G11" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>381</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>15</v>
@@ -4861,24 +4920,24 @@
         <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>15</v>
@@ -4887,15 +4946,15 @@
         <v>53</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>28</v>
@@ -4913,21 +4972,21 @@
         <v>165</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>7</v>
@@ -4939,15 +4998,15 @@
         <v>16</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>28</v>
@@ -4956,24 +5015,24 @@
         <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>28</v>
@@ -4982,85 +5041,85 @@
         <v>15</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>365</v>
+        <v>7</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>403</v>
-      </c>
       <c r="F19" s="10" t="s">
-        <v>404</v>
+        <v>53</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>15</v>
@@ -5069,15 +5128,15 @@
         <v>53</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>28</v>
@@ -5086,61 +5145,113 @@
         <v>15</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>413</v>
-      </c>
       <c r="F22" s="5" t="s">
-        <v>414</v>
+        <v>53</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H22"/>
+  <autoFilter ref="A4:H24"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -5173,7 +5284,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5182,7 +5293,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5191,602 +5302,602 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>

--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">GLOSSARIO!$A$4:$E$38</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$24</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$45</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$25</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$52</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="635">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -645,6 +645,99 @@
     <t xml:space="preserve">Hoje o exame do cliente e guardado no Google Drive. Isso faz o sistema guardar TAMBEM num deposito de arquivos mais barato, com o nome ja saindo organizado na gravacao. O Drive continua igual: e espelho, nao troca. Serve para voce ver um item nascer, andar e fechar usando a nossa propria ferramenta.</t>
   </si>
   <si>
+    <t xml:space="preserve">Extracao da Central de IA para fora do clone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item D da carta do Dr. Replit. Tirar a central de IA de dentro do clone para o modelo de negocio nao quebrar no primeiro licenciado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a definir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrou como 42 e nao como 41: o 41 ja e a rota de upload do paciente desde 30/07. Detalhe em docs/dr-replit/CARTA_DR_CODE_CLOUDFLARE_R2_26.07.30.md, commit 670fcf5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoje a central de inteligencia artificial mora dentro da copia do sistema. Ao vender para a primeira clinica, ela iria junto — e o motor que voce cobra viraria de graca. Isso tira a central para fora.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Gateway como proxy unico de IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item A da carta. Toda chamada de IA passa por um lugar so, que conta token por clinica. Ideia do CEO, desenho do Dr. Replit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melhor que contar evento dentro do codigo: medidor na entrada nao pode ser esquecido. Analogia do CEO: caixa de energia na frente da casa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toda conversa com inteligencia artificial passa a atravessar um unico portao que conta quanto cada clinica gastou. E a caixa de energia na frente da casa: nada consome sem passar pelo medidor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ledger billing_events com job noturno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item B da carta. Tabela de eventos de cobranca no Postgres, alimentada todo dia pela leitura do AI Gateway.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBRIGATORIO para nao depender do fornecedor: o Cloudflare mede, mas quem guarda o historico de faturamento tem de ser o banco do CEO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A leitura do medidor e copiada todo dia para o SEU banco. Sem isso o historico de cobranca fica na mao do fornecedor, e voce depende dele para provar quanto cada clinica usou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circuit breaker por saldo antes do fornecedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item C da carta. Bloqueia a clinica sem saldo ANTES de gastar token no fornecedor de IA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protege a margem do CEO, nao a do fornecedor. E o disjuntor do quadro, na analogia do CEO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O disjuntor: corta a clinica que nao tem saldo ANTES de gastar dinheiro com o fornecedor. Sem ele, cliente inadimplente consome e a conta e sua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatura mensal automatica no Asaas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item E da carta. Geracao mensal com descricao itemizada por consumo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So depois do ledger: fatura sem historico proprio e fatura que nao se defende.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A fatura do mes sai sozinha, com cada linha discriminada, igual conta de luz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painel de prova de valor para o CEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item F da carta. Leitura pura de dado que ja existe no banco. Argumento de venda para o primeiro licenciado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nao depende de nada: o dado ja esta no banco. Item de maior retorno por hora de trabalho da carta inteira.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma tela mostrando quanto valor o sistema ja entregou. O dado ja existe no banco: e so ler. E o que voce mostra na reuniao de venda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trava de royalty em um nivel so</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item G da carta. Assert no codigo garantindo que indicacao paga um nivel e nao vira cadeia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evita virar marketing multinivel por acidente, o que traria risco juridico que o CEO nao pediu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garante que indicacao paga UM nivel so. Sem essa trava, o programa de indicacao vira pirâmide por acidente, e isso traz problema juridico.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rota de upload na area do paciente</t>
   </si>
   <si>
@@ -798,9 +891,6 @@
     <t xml:space="preserve">VAGA 1 — a definir</t>
   </si>
   <si>
-    <t xml:space="preserve">a definir</t>
-  </si>
-  <si>
     <t xml:space="preserve">A definir no ritual de entrada</t>
   </si>
   <si>
@@ -1243,6 +1333,15 @@
   </si>
   <si>
     <t xml:space="preserve">Dr. Chat (ChatGPT) entrou no quadro por decisao do CEO. Territorio escolhido para NAO sobrepor ninguem: peca avulsa e auditoria independente, entregue na doca, sem commitar. Modelo de familia diferente lendo a mesma spec pega o que o autor nao viu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sete itens da carta do Dr. Replit (commit 670fcf5) absorvidos. Ele numerou 41 a 47; entraram como 42 a 48 porque o 41 ja e a rota de upload do paciente desde a manha. QUARTA vez que numero em uso foi reaproveitado — nada dele foi perdido, so renumerado para cima.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit 670fcf5</t>
   </si>
   <si>
     <t xml:space="preserve">40</t>
@@ -2414,7 +2513,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3707,7 +3806,7 @@
     </row>
     <row r="43" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>204</v>
@@ -3725,30 +3824,30 @@
         <v>53</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>60</v>
+        <v>206</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>15</v>
@@ -3757,103 +3856,327 @@
         <v>53</v>
       </c>
       <c r="G44" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H46" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="n">
+      <c r="I51" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="B52" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E52" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F52" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G52" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H52" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C48" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F45,"CONCLUIDO")</f>
+      <c r="I52" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <f aca="false">COUNTIF(F5:F52,"CONCLUIDO")</f>
         <v>11</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="C49" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F45,"A FAZER")</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C50" s="9" t="n">
-        <f aca="false">COUNTIF(F5:F45,"AGUARDANDO")</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="C51" s="9" t="n">
-        <f aca="false">COUNTA(A5:A45)</f>
-        <v>41</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <f aca="false">COUNTIF(F5:F52,"A FAZER")</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <f aca="false">COUNTIF(F5:F52,"AGUARDANDO")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <f aca="false">COUNTA(A5:A52)</f>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J45"/>
+  <autoFilter ref="A4:J52"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F45" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F52" type="list">
       <formula1>"A FAZER,EM CURSO,AGUARDANDO,CONCLUIDO,CANCELADO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G45" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G52" type="list">
       <formula1>"P0 critico,P1 alto,P2 medio,P3 baixo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3885,7 +4208,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3894,7 +4217,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3903,19 +4226,19 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3923,16 +4246,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3940,33 +4263,33 @@
         <v>28</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3974,16 +4297,16 @@
         <v>43</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3991,94 +4314,94 @@
         <v>165</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4087,7 +4410,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4096,7 +4419,7 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4105,7 +4428,7 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4114,7 +4437,7 @@
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4158,7 +4481,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4167,7 +4490,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4179,16 +4502,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4196,13 +4519,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -4211,13 +4534,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -4226,10 +4549,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>122</v>
@@ -4241,10 +4564,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>122</v>
@@ -4256,13 +4579,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -4271,13 +4594,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -4286,13 +4609,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -4301,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -4316,13 +4639,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -4331,36 +4654,36 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -4392,78 +4715,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4496,7 +4819,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4504,7 +4827,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4512,128 +4835,128 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4656,7 +4979,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -4670,7 +4993,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4682,7 +5005,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4694,33 +5017,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>28</v>
@@ -4729,30 +5052,30 @@
         <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
@@ -4764,15 +5087,15 @@
         <v>53</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>28</v>
@@ -4790,21 +5113,21 @@
         <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
@@ -4816,15 +5139,15 @@
         <v>87</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -4842,21 +5165,21 @@
         <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>7</v>
@@ -4868,21 +5191,21 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
@@ -4894,24 +5217,24 @@
         <v>53</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>15</v>
@@ -4920,24 +5243,24 @@
         <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>15</v>
@@ -4946,15 +5269,15 @@
         <v>53</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>28</v>
@@ -4972,21 +5295,21 @@
         <v>165</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>7</v>
@@ -4998,15 +5321,15 @@
         <v>16</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>28</v>
@@ -5015,24 +5338,24 @@
         <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>28</v>
@@ -5041,85 +5364,85 @@
         <v>15</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>403</v>
+        <v>433</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>7</v>
+        <v>399</v>
       </c>
       <c r="E18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="G18" s="5" t="s">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>369</v>
+        <v>7</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>15</v>
@@ -5128,93 +5451,93 @@
         <v>53</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>412</v>
-      </c>
       <c r="F21" s="10" t="s">
-        <v>413</v>
+        <v>53</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>416</v>
+        <v>15</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>369</v>
+        <v>444</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>15</v>
+        <v>445</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>53</v>
+        <v>446</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>402</v>
-      </c>
       <c r="F23" s="10" t="s">
-        <v>419</v>
+        <v>53</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>392</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>28</v>
@@ -5223,35 +5546,61 @@
         <v>15</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
+    </row>
+    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H24"/>
+  <autoFilter ref="A4:H25"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -5284,7 +5633,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5293,7 +5642,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5302,602 +5651,602 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>429</v>
+        <v>462</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>436</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>438</v>
+        <v>471</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>445</v>
+        <v>478</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>446</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>447</v>
+        <v>480</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>452</v>
+        <v>485</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>456</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>457</v>
+        <v>490</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>465</v>
+        <v>498</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>466</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>468</v>
+        <v>501</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>469</v>
+        <v>502</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>470</v>
+        <v>503</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>471</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>474</v>
+        <v>507</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>475</v>
+        <v>508</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>476</v>
+        <v>509</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>478</v>
+        <v>511</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>480</v>
+        <v>513</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>481</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>482</v>
+        <v>515</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>484</v>
+        <v>517</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>485</v>
+        <v>518</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>486</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>487</v>
+        <v>520</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>488</v>
+        <v>521</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>489</v>
+        <v>522</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>490</v>
+        <v>523</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>491</v>
+        <v>524</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>492</v>
+        <v>525</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>493</v>
+        <v>526</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>494</v>
+        <v>527</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>495</v>
+        <v>528</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>496</v>
+        <v>529</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>497</v>
+        <v>530</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>498</v>
+        <v>531</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>500</v>
+        <v>533</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>501</v>
+        <v>534</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>502</v>
+        <v>535</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>503</v>
+        <v>536</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>511</v>
+        <v>544</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>515</v>
+        <v>548</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>516</v>
+        <v>549</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>517</v>
+        <v>550</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>518</v>
+        <v>551</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>519</v>
+        <v>552</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>520</v>
+        <v>553</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>521</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>522</v>
+        <v>555</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>524</v>
+        <v>557</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>525</v>
+        <v>558</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>526</v>
+        <v>559</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>527</v>
+        <v>560</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>528</v>
+        <v>561</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>529</v>
+        <v>562</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>530</v>
+        <v>563</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>531</v>
+        <v>564</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>532</v>
+        <v>565</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>533</v>
+        <v>566</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>534</v>
+        <v>567</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>535</v>
+        <v>568</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>538</v>
+        <v>571</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>540</v>
+        <v>573</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>541</v>
+        <v>574</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>542</v>
+        <v>575</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>544</v>
+        <v>577</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>545</v>
+        <v>578</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>546</v>
+        <v>579</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>547</v>
+        <v>580</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>548</v>
+        <v>581</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>549</v>
+        <v>582</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>550</v>
+        <v>583</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>551</v>
+        <v>584</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>553</v>
+        <v>586</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>554</v>
+        <v>587</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>555</v>
+        <v>588</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>556</v>
+        <v>589</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>557</v>
+        <v>590</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>560</v>
+        <v>593</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>561</v>
+        <v>594</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>562</v>
+        <v>595</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>563</v>
+        <v>596</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>565</v>
+        <v>598</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>566</v>
+        <v>599</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>567</v>
+        <v>600</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>568</v>
+        <v>601</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>570</v>
+        <v>603</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>571</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>572</v>
+        <v>605</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>573</v>
+        <v>606</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>574</v>
+        <v>607</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>575</v>
+        <v>608</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>576</v>
+        <v>609</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>578</v>
+        <v>611</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>579</v>
+        <v>612</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>580</v>
+        <v>613</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>581</v>
+        <v>614</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>582</v>
+        <v>615</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>584</v>
+        <v>617</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>585</v>
+        <v>618</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>586</v>
+        <v>619</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>587</v>
+        <v>620</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>588</v>
+        <v>621</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>589</v>
+        <v>622</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>590</v>
+        <v>623</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>591</v>
+        <v>624</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>592</v>
+        <v>625</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>593</v>
+        <v>626</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>599</v>
+        <v>632</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>600</v>
+        <v>633</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>601</v>
+        <v>634</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>425</v>
+        <v>458</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>

--- a/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
+++ b/docs/LINHA_DE_PRODUCAO/PADAXOR_LINHA_DE_PRODUCAO_26.07.29.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">GLOSSARIO!$A$4:$E$38</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$25</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">HISTORICO!$A$4:$H$26</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'LINHA DE PRODUCAO'!$A$4:$J$52</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="640">
   <si>
     <t xml:space="preserve">PADAXOR — Linha de Producao</t>
   </si>
@@ -228,264 +228,267 @@
     <t xml:space="preserve">scrypt-col$ e scrypt-pac$, com recusa ruidosa do prefixo errado.</t>
   </si>
   <si>
+    <t xml:space="preserve">fase 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FASE 1 entregue 30/07 no commit df4c998, 18 conferencias passando. Grava scrypt-col$ e scrypt-pac$, LE o scrypt$ antigo com a derivacao historica de cada esquema — ninguem trancado fora. Rotulo do outro esquema tem recusa ruidosa. FASE 2 (parar de aceitar scrypt$) e decisao do CEO, so quando nao houver mais hash antigo. NAO PUBLICADO: aguarda validacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existem dois tipos de senha no sistema, guardados de jeitos diferentes, mas gravados com a MESMA etiqueta. E como dois frascos de remedio com o mesmo rotulo e conteudo diferente. Foi isso que fez seu login falhar por uma noite inteira. Isso poe rotulo diferente em cada frasco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela de login dentro do padaxor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela propria chamando /api/collaborator/login e setCollabSession. O encanamento ja existe em collab-auth.ts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregue 30/07 no commit 3a38349, conferido: pages/login/index.tsx criado e CollaboratorGate passou a redirecionar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela de entrada propria do sistema, em vez da caixinha cinza do navegador. Ja entregue em 30/07.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site vira botao, nao segundo login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O login do site aponta para a tela do sistema em vez de autenticar por conta propria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIBERADO em 30/07: a tela do item 11 existe. Elimina o segundo formulario de autenticacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O botao Entrar do site deixa de pedir senha por conta propria e passa a levar a pessoa para a tela de entrada do sistema. Uma porta so em vez de duas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNS do padaxor.com.br no Cloudflare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar os servidores de nome no Registro.br pelos do Cloudflare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Railway exige CNAME Flattening ou ALIAS para dominio raiz. Registro.br nao faz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar quem cuida do endereco padaxor.com.br na internet. O registrador brasileiro nao faz um recurso que o servidor precisa; o Cloudflare faz, e e de graca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominio proprio apontando para o sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">app.padaxor.com.br no Railway com certificado automatico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUARDANDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depende do passo do Cloudflare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fazer app.padaxor.com.br apontar para o sistema, com cadeado de seguranca automatico no navegador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca PAXTER para PADAXOR no painel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O painel do sistema ainda exibe PAXTER na identidade visual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parcial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titulo da aba e do aplicativo entregues 30/07 no commit 3a38349. As telas internas seguem no item 38.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O painel ainda mostrava o nome antigo PAXTER. Titulo da aba corrigido em 30/07; o resto das telas segue no item 38.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porta da area do paciente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O site nao tem entrada para /api/area-paciente, que tem 12 rotas prontas no servidor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarta porta do produto inteira sem macaneta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O servidor ja tem doze portas prontas para a area do paciente, mas o site nao tem nenhum botao que leve ate elas. E uma porta inteira construida e sem macaneta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indice unico em lower(login_username)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impede dois colaboradores com o mesmo usuario. Erro 23505 traduzido em 409.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prevencao. Nao foi a causa do bug de hoje — nao havia duplicata.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impedir que dois colaboradores tenham o mesmo nome de usuario. Prevencao: nao foi a causa do problema de hoje, mas seria a causa do de amanha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligar o registro de consumo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comecar a gravar em consumo_eventos, que ja existe com empresa_id, custo e idempotencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2 medio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem historico nao ha painel. Historico nao se cria retroativamente. Espera o RLS do Dr. Code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comecar a anotar quanto cada clinica usa do sistema. Sem anotar desde ja, nao existe historico depois: historico nao se cria para tras.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalogo de modulos com precos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabela de modulos: nome, beneficio, valor de adesao, valor promocional, mensalidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decisao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os valores sao decisao do CEO. Nada vai para tela sem eles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definir quanto custa cada modulo em reais. So voce decide. Nenhum preco vai para tela sem isso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menu com modulos travados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itens nao comprados aparecem apagados com cadeado. Clique abre a mensagem de desejo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coracao do modelo comercial. Depende do catalogo e dos precos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os modulos que a clinica nao comprou aparecem apagados com um cadeado, e clicar abre a oferta. E a vitrine da loja: voce ve o que nao comprou, e isso e o que faz querer comprar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mensagem de desejo com 48h e indicacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descricao do beneficio, preco promocional valido 48h, valor cheio riscado, 10% por indicacao na adesao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mensalidade nunca muda — desconto so na entrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A mensagem que aparece ao clicar no cadeado: o que o modulo faz, o preco promocional valendo 48 horas, o valor cheio riscado e o desconto por indicacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login de licenciado (o segundo chapeu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segundo usuario do CEO, entrando na mesma clinica com a visao travada do cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dois logins, mesma clinica, lentes diferentes. Pagamento real de R$ 1 via Asaas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um segundo usuario seu, entrando na mesma clinica, mas enxergando so o que um cliente enxergaria. Dois cracha, mesma porta, oculos diferentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painel do CEO com seletor de clinica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visao consolidada de todas as clinicas e troca de contexto para ver como o dono ve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tenantContext ja modela isPlatformOwner + empresaId. Comecar somente-leitura nas outras clinicas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painel onde voce ve todas as clinicas de uma vez e consegue entrar na visao de cada dona para ver o que ela ve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painel de bilhetagem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumo por clinica, por periodo, por tipo. Atualizacao por LISTEN/NOTIFY do Postgres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem fornecedor novo. Com 12 clinicas o Postgres aguenta com folga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painel de quanto cada clinica consumiu, por periodo e por tipo, atualizando sozinho na tela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upsell por limiar de uso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regra por modulo: metrica, limiar, mensagem, desconto. Dispara apos cada evento de consumo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oferece quando o uso prova que faz sentido. Observacao honesta, nao pressao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando o uso de um modulo passa de um limite, o sistema oferece o upgrade sozinho. Oferece quando o proprio uso ja provou que faz sentido, nao antes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho configurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOHO_ORG_ID e token de admin nas variaveis. Codigo de criacao de conta e alias ja existe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precisa da conta Zoho e do token. Depois disso o sistema cria sozinho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurar a conta de e-mail corporativo. Depois disso o sistema cria os e-mails de cada clinica nova sozinho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNS automatico via Cloudflare API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ao ativar uma clinica, o sistema cria os registros de DNS sem ninguem tocar no painel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">3h</t>
   </si>
   <si>
-    <t xml:space="preserve">Os dois gravam scrypt$ hoje. Foi a armadilha que custou uma noite inteira.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existem dois tipos de senha no sistema, guardados de jeitos diferentes, mas gravados com a MESMA etiqueta. E como dois frascos de remedio com o mesmo rotulo e conteudo diferente. Foi isso que fez seu login falhar por uma noite inteira. Isso poe rotulo diferente em cada frasco.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tela de login dentro do padaxor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tela propria chamando /api/collaborator/login e setCollabSession. O encanamento ja existe em collab-auth.ts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entregue 30/07 no commit 3a38349, conferido: pages/login/index.tsx criado e CollaboratorGate passou a redirecionar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tela de entrada propria do sistema, em vez da caixinha cinza do navegador. Ja entregue em 30/07.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site vira botao, nao segundo login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O login do site aponta para a tela do sistema em vez de autenticar por conta propria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIBERADO em 30/07: a tela do item 11 existe. Elimina o segundo formulario de autenticacao.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O botao Entrar do site deixa de pedir senha por conta propria e passa a levar a pessoa para a tela de entrada do sistema. Uma porta so em vez de duas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNS do padaxor.com.br no Cloudflare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar os servidores de nome no Registro.br pelos do Cloudflare.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Railway exige CNAME Flattening ou ALIAS para dominio raiz. Registro.br nao faz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar quem cuida do endereco padaxor.com.br na internet. O registrador brasileiro nao faz um recurso que o servidor precisa; o Cloudflare faz, e e de graca.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominio proprio apontando para o sistema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">app.padaxor.com.br no Railway com certificado automatico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGUARDANDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depende do passo do Cloudflare.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fazer app.padaxor.com.br apontar para o sistema, com cadeado de seguranca automatico no navegador.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marca PAXTER para PADAXOR no painel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O painel do sistema ainda exibe PAXTER na identidade visual.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parcial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titulo da aba e do aplicativo entregues 30/07 no commit 3a38349. As telas internas seguem no item 38.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O painel ainda mostrava o nome antigo PAXTER. Titulo da aba corrigido em 30/07; o resto das telas segue no item 38.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porta da area do paciente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O site nao tem entrada para /api/area-paciente, que tem 12 rotas prontas no servidor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quarta porta do produto inteira sem macaneta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O servidor ja tem doze portas prontas para a area do paciente, mas o site nao tem nenhum botao que leve ate elas. E uma porta inteira construida e sem macaneta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indice unico em lower(login_username)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impede dois colaboradores com o mesmo usuario. Erro 23505 traduzido em 409.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prevencao. Nao foi a causa do bug de hoje — nao havia duplicata.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impedir que dois colaboradores tenham o mesmo nome de usuario. Prevencao: nao foi a causa do problema de hoje, mas seria a causa do de amanha.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ligar o registro de consumo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comecar a gravar em consumo_eventos, que ja existe com empresa_id, custo e idempotencia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2 medio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sem historico nao ha painel. Historico nao se cria retroativamente. Espera o RLS do Dr. Code.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comecar a anotar quanto cada clinica usa do sistema. Sem anotar desde ja, nao existe historico depois: historico nao se cria para tras.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalogo de modulos com precos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabela de modulos: nome, beneficio, valor de adesao, valor promocional, mensalidade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decisao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Os valores sao decisao do CEO. Nada vai para tela sem eles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definir quanto custa cada modulo em reais. So voce decide. Nenhum preco vai para tela sem isso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menu com modulos travados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Itens nao comprados aparecem apagados com cadeado. Clique abre a mensagem de desejo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coracao do modelo comercial. Depende do catalogo e dos precos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Os modulos que a clinica nao comprou aparecem apagados com um cadeado, e clicar abre a oferta. E a vitrine da loja: voce ve o que nao comprou, e isso e o que faz querer comprar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensagem de desejo com 48h e indicacao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descricao do beneficio, preco promocional valido 48h, valor cheio riscado, 10% por indicacao na adesao.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensalidade nunca muda — desconto so na entrada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A mensagem que aparece ao clicar no cadeado: o que o modulo faz, o preco promocional valendo 48 horas, o valor cheio riscado e o desconto por indicacao.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login de licenciado (o segundo chapeu)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segundo usuario do CEO, entrando na mesma clinica com a visao travada do cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dois logins, mesma clinica, lentes diferentes. Pagamento real de R$ 1 via Asaas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Um segundo usuario seu, entrando na mesma clinica, mas enxergando so o que um cliente enxergaria. Dois cracha, mesma porta, oculos diferentes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Painel do CEO com seletor de clinica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visao consolidada de todas as clinicas e troca de contexto para ver como o dono ve.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tenantContext ja modela isPlatformOwner + empresaId. Comecar somente-leitura nas outras clinicas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Painel onde voce ve todas as clinicas de uma vez e consegue entrar na visao de cada dona para ver o que ela ve.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Painel de bilhetagem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumo por clinica, por periodo, por tipo. Atualizacao por LISTEN/NOTIFY do Postgres.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 dias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sem fornecedor novo. Com 12 clinicas o Postgres aguenta com folga.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Painel de quanto cada clinica consumiu, por periodo e por tipo, atualizando sozinho na tela.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upsell por limiar de uso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regra por modulo: metrica, limiar, mensagem, desconto. Dispara apos cada evento de consumo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oferece quando o uso prova que faz sentido. Observacao honesta, nao pressao.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quando o uso de um modulo passa de um limite, o sistema oferece o upgrade sozinho. Oferece quando o proprio uso ja provou que faz sentido, nao antes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho configurado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOHO_ORG_ID e token de admin nas variaveis. Codigo de criacao de conta e alias ja existe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precisa da conta Zoho e do token. Depois disso o sistema cria sozinho.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configurar a conta de e-mail corporativo. Depois disso o sistema cria os e-mails de cada clinica nova sozinho.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNS automatico via Cloudflare API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ao ativar uma clinica, o sistema cria os registros de DNS sem ninguem tocar no painel.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Depende do Cloudflare ser o provedor de DNS.</t>
   </si>
   <si>
@@ -1333,6 +1336,18 @@
   </si>
   <si>
     <t xml:space="preserve">Dr. Chat (ChatGPT) entrou no quadro por decisao do CEO. Territorio escolhido para NAO sobrepor ninguem: peca avulsa e auditoria independente, entregue na doca, sem commitar. Modelo de familia diferente lendo a mesma spec pega o que o autor nao viu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCLUIDO (fase 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Causa raiz PROVADA por teste, nao por leitura: os dois esquemas gravavam scrypt$ e derivavam de formas incompativeis, um entregando o salt como string e o outro como buffer. O teste 1 do commit df4c998 demonstra chaves diferentes para mesmo salt e mesma senha. Corrigido sem regravar nenhuma senha: mudou o rotulo, nao a derivacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit df4c998</t>
   </si>
   <si>
     <t xml:space="preserve">42-48</t>
@@ -2877,34 +2892,34 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="F14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="4" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3443,13 +3458,13 @@
         <v>107</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3457,16 +3472,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>87</v>
@@ -3475,13 +3490,13 @@
         <v>107</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3489,10 +3504,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
@@ -3510,10 +3525,10 @@
         <v>54</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3521,13 +3536,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>15</v>
@@ -3536,16 +3551,16 @@
         <v>53</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>97</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3553,31 +3568,31 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>97</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3585,10 +3600,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>28</v>
@@ -3600,16 +3615,16 @@
         <v>53</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3617,31 +3632,31 @@
         <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>60</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3649,10 +3664,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>23</v>
@@ -3664,16 +3679,16 @@
         <v>53</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>112</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3681,10 +3696,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>28</v>
@@ -3696,16 +3711,16 @@
         <v>53</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>60</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3713,13 +3728,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>15</v>
@@ -3728,16 +3743,16 @@
         <v>16</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3745,10 +3760,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
@@ -3766,10 +3781,10 @@
         <v>60</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3777,10 +3792,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>14</v>
@@ -3798,10 +3813,10 @@
         <v>18</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3809,10 +3824,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>14</v>
@@ -3827,13 +3842,13 @@
         <v>17</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3841,10 +3856,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>14</v>
@@ -3859,13 +3874,13 @@
         <v>44</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3873,16 +3888,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>87</v>
@@ -3891,13 +3906,13 @@
         <v>44</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3905,16 +3920,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>87</v>
@@ -3923,13 +3938,13 @@
         <v>107</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3937,16 +3952,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>87</v>
@@ -3955,13 +3970,13 @@
         <v>107</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3969,10 +3984,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>14</v>
@@ -3987,13 +4002,13 @@
         <v>44</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4001,10 +4016,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>28</v>
@@ -4022,10 +4037,10 @@
         <v>54</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4033,10 +4048,10 @@
         <v>41</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>14</v>
@@ -4054,10 +4069,10 @@
         <v>60</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4065,10 +4080,10 @@
         <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>28</v>
@@ -4083,13 +4098,13 @@
         <v>107</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4097,10 +4112,10 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>14</v>
@@ -4115,41 +4130,41 @@
         <v>44</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C55" s="9" t="n">
         <f aca="false">COUNTIF(F5:F52,"CONCLUIDO")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C56" s="9" t="n">
         <f aca="false">COUNTIF(F5:F52,"A FAZER")</f>
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C57" s="9" t="n">
         <f aca="false">COUNTIF(F5:F52,"AGUARDANDO")</f>
@@ -4158,7 +4173,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C58" s="9" t="n">
         <f aca="false">COUNTA(A5:A52)</f>
@@ -4208,7 +4223,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4217,7 +4232,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4226,19 +4241,19 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4246,16 +4261,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4263,33 +4278,33 @@
         <v>28</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4297,111 +4312,111 @@
         <v>43</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4410,7 +4425,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4419,7 +4434,7 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4428,7 +4443,7 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4437,7 +4452,7 @@
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4481,7 +4496,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4490,7 +4505,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4502,16 +4517,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4519,13 +4534,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -4534,13 +4549,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -4549,10 +4564,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>122</v>
@@ -4564,10 +4579,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>122</v>
@@ -4579,13 +4594,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -4594,13 +4609,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -4609,13 +4624,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -4624,13 +4639,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -4639,13 +4654,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -4654,36 +4669,36 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -4715,78 +4730,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -4819,7 +4834,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4827,7 +4842,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4835,128 +4850,128 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -4979,7 +4994,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -4993,7 +5008,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5005,7 +5020,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5017,33 +5032,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>28</v>
@@ -5052,30 +5067,30 @@
         <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
@@ -5087,15 +5102,15 @@
         <v>53</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>28</v>
@@ -5113,21 +5128,21 @@
         <v>87</v>
       </c>
       <c r="G7" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>406</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
@@ -5139,15 +5154,15 @@
         <v>87</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -5165,21 +5180,21 @@
         <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>7</v>
@@ -5191,21 +5206,21 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
@@ -5217,24 +5232,24 @@
         <v>53</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>15</v>
@@ -5243,24 +5258,24 @@
         <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>15</v>
@@ -5269,21 +5284,21 @@
         <v>53</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>5</v>
@@ -5292,24 +5307,24 @@
         <v>28</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>7</v>
@@ -5321,15 +5336,15 @@
         <v>16</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>28</v>
@@ -5338,24 +5353,24 @@
         <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>28</v>
@@ -5364,111 +5379,111 @@
         <v>15</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>399</v>
+        <v>7</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>53</v>
+        <v>436</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>7</v>
+        <v>400</v>
       </c>
       <c r="E19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>16</v>
-      </c>
       <c r="G19" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>399</v>
+        <v>7</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>15</v>
@@ -5477,93 +5492,93 @@
         <v>53</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>445</v>
-      </c>
       <c r="F22" s="5" t="s">
-        <v>446</v>
+        <v>53</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>399</v>
-      </c>
       <c r="E23" s="10" t="s">
-        <v>15</v>
+        <v>450</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>53</v>
+        <v>451</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>432</v>
-      </c>
       <c r="F24" s="5" t="s">
-        <v>452</v>
+        <v>53</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>28</v>
@@ -5572,35 +5587,61 @@
         <v>15</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
-        <v>458</v>
-      </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H25"/>
+  <autoFilter ref="A4:H26"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -5633,7 +5674,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5642,7 +5683,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5651,602 +5692,602 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
